--- a/data/trans_orig/IP07A16-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP07A16-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de ayudarse entre los amigos en 2007 (tasa de respuesta: 99,2%)</t>
+          <t>Menores según la frecuencia de ayudarse entre los/as amigos/as, percibida por el adulto en 2007 (tasa de respuesta: 99,2%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20098</t>
+          <t>19824</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30771</t>
+          <t>30835</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>40,16%</t>
+          <t>39,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>61,49%</t>
+          <t>61,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19647</t>
+          <t>19362</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30700</t>
+          <t>30141</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>41,6%</t>
+          <t>41,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>65,0%</t>
+          <t>63,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>42769</t>
+          <t>43194</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>58885</t>
+          <t>58866</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>43,97%</t>
+          <t>44,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>60,54%</t>
+          <t>60,52%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14726</t>
+          <t>14230</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25581</t>
+          <t>25569</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>51,12%</t>
+          <t>51,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13870</t>
+          <t>13649</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24528</t>
+          <t>24994</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>51,93%</t>
+          <t>52,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>30664</t>
+          <t>30867</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>46919</t>
+          <t>46749</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>48,23%</t>
+          <t>48,06%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1523</t>
+          <t>1360</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8193</t>
+          <t>8365</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1359</t>
+          <t>1361</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6947</t>
+          <t>7543</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4023</t>
+          <t>4027</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>12743</t>
+          <t>13256</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,63%</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3397</t>
+          <t>3432</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>3446</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,54%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>92799</t>
+          <t>92649</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>115004</t>
+          <t>115333</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>45,79%</t>
+          <t>45,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>56,74%</t>
+          <t>56,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>103306</t>
+          <t>104033</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>129139</t>
+          <t>128741</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>43,54%</t>
+          <t>43,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>54,43%</t>
+          <t>54,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>203985</t>
+          <t>202844</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>236585</t>
+          <t>236535</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>46,37%</t>
+          <t>46,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>53,78%</t>
+          <t>53,77%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>63992</t>
+          <t>64151</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>86061</t>
+          <t>84474</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>42,46%</t>
+          <t>41,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>85881</t>
+          <t>86333</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>111667</t>
+          <t>110123</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>36,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>47,06%</t>
+          <t>46,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>155470</t>
+          <t>155344</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>188914</t>
+          <t>189588</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>35,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,94%</t>
+          <t>43,09%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16051</t>
+          <t>16172</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>30562</t>
+          <t>30772</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>15409</t>
+          <t>15596</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>30180</t>
+          <t>30429</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>36062</t>
+          <t>34736</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>55627</t>
+          <t>55363</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,58%</t>
         </is>
       </c>
     </row>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4176</t>
+          <t>3992</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3156</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>487</t>
+          <t>489</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5266</t>
+          <t>4996</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,14%</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3712</t>
+          <t>3258</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3248</t>
+          <t>3879</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4184</t>
+          <t>4928</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18620</t>
+          <t>18746</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>31308</t>
+          <t>31534</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>46,83%</t>
+          <t>47,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18511</t>
+          <t>18227</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30433</t>
+          <t>30510</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>50,94%</t>
+          <t>51,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>39743</t>
+          <t>40487</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>57801</t>
+          <t>57951</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>45,66%</t>
+          <t>45,78%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>25441</t>
+          <t>25435</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>38715</t>
+          <t>38773</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>57,91%</t>
+          <t>58,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>22565</t>
+          <t>22106</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>34815</t>
+          <t>34821</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>37,77%</t>
+          <t>37,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>58,27%</t>
+          <t>58,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>50533</t>
+          <t>51290</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>68912</t>
+          <t>69027</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>39,92%</t>
+          <t>40,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>54,43%</t>
+          <t>54,52%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5772</t>
+          <t>5868</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15204</t>
+          <t>15009</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3701</t>
+          <t>3478</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11596</t>
+          <t>11767</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>11221</t>
+          <t>10974</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>23912</t>
+          <t>24139</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>19,07%</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3449</t>
+          <t>3208</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4191</t>
+          <t>2927</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>141217</t>
+          <t>141130</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>170193</t>
+          <t>170443</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>44,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>53,26%</t>
+          <t>53,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>151318</t>
+          <t>150567</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>179244</t>
+          <t>180296</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>43,96%</t>
+          <t>43,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>52,07%</t>
+          <t>52,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>298967</t>
+          <t>299590</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>342634</t>
+          <t>341172</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>45,04%</t>
+          <t>45,13%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>51,62%</t>
+          <t>51,4%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>111637</t>
+          <t>111218</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>139724</t>
+          <t>139471</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>43,72%</t>
+          <t>43,64%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>131597</t>
+          <t>129794</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>159695</t>
+          <t>159506</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>37,7%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>46,34%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>248607</t>
+          <t>250093</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>292369</t>
+          <t>292935</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>37,68%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>44,04%</t>
+          <t>44,13%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>27038</t>
+          <t>27152</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>46715</t>
+          <t>45400</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>24157</t>
+          <t>24018</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>42223</t>
+          <t>40815</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>56279</t>
+          <t>56509</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>80962</t>
+          <t>81764</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,32%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>689</t>
+          <t>686</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6411</t>
+          <t>6035</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2446</t>
+          <t>3123</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1182</t>
+          <t>1143</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6832</t>
+          <t>7208</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,09%</t>
         </is>
       </c>
     </row>
@@ -3235,7 +3235,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3169</t>
+          <t>3788</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,7 +3250,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,7 +3270,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3865</t>
+          <t>3256</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,7 +3305,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4490</t>
+          <t>5113</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de ayudarse entre los amigos en 2012 (tasa de respuesta: 97,81%)</t>
+          <t>Menores según la frecuencia de ayudarse entre los/as amigos/as, percibida por el adulto en 2012 (tasa de respuesta: 97,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22310</t>
+          <t>22229</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34760</t>
+          <t>34651</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>42,61%</t>
+          <t>42,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>66,38%</t>
+          <t>66,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18336</t>
+          <t>18669</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29797</t>
+          <t>29345</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>39,99%</t>
+          <t>40,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>64,98%</t>
+          <t>64,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>44403</t>
+          <t>44261</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>61207</t>
+          <t>60747</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>45,21%</t>
+          <t>45,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>62,32%</t>
+          <t>61,85%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11029</t>
+          <t>11140</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22289</t>
+          <t>22021</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>42,57%</t>
+          <t>42,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13013</t>
+          <t>13598</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24404</t>
+          <t>24186</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>53,22%</t>
+          <t>52,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>26961</t>
+          <t>27232</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>43354</t>
+          <t>43389</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>44,18%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2333</t>
+          <t>2514</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10376</t>
+          <t>10496</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1228</t>
+          <t>1236</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6893</t>
+          <t>6538</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4550</t>
+          <t>4666</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>14580</t>
+          <t>13835</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,09%</t>
         </is>
       </c>
     </row>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6084</t>
+          <t>6188</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4050,7 +4050,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4105,7 +4105,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5712</t>
+          <t>6083</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>6,19%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>84112</t>
+          <t>85282</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>107053</t>
+          <t>108609</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>41,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>52,11%</t>
+          <t>52,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>104220</t>
+          <t>105254</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>129935</t>
+          <t>131498</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>45,83%</t>
+          <t>46,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>57,14%</t>
+          <t>57,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>197918</t>
+          <t>197026</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>232590</t>
+          <t>231727</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>45,73%</t>
+          <t>45,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>53,74%</t>
+          <t>53,54%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>81578</t>
+          <t>78578</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>103479</t>
+          <t>103007</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>38,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>50,38%</t>
+          <t>50,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>73946</t>
+          <t>72133</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>98783</t>
+          <t>97859</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>43,44%</t>
+          <t>43,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>159336</t>
+          <t>160098</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>193809</t>
+          <t>196147</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>36,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>45,32%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7837</t>
+          <t>7560</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18466</t>
+          <t>18578</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4614,47 +4614,47 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
+          <t>9,04%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>20439</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>14160</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>28047</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
           <t>8,99%</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>20439</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>14341</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>28059</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>8,99%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>24420</t>
+          <t>24601</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>43074</t>
+          <t>42502</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,82%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>740</t>
+          <t>702</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6599</t>
+          <t>6623</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>845</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6713</t>
+          <t>6158</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2246</t>
+          <t>2493</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9948</t>
+          <t>10817</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>666</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6298</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4845,7 +4845,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4865,7 +4865,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4008</t>
+          <t>4492</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>1312</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>8348</t>
+          <t>8415</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4915,7 +4915,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29414</t>
+          <t>28006</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>42292</t>
+          <t>42022</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>46,38%</t>
+          <t>44,16%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>66,69%</t>
+          <t>66,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27510</t>
+          <t>27433</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>39515</t>
+          <t>40068</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>47,49%</t>
+          <t>47,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>68,21%</t>
+          <t>69,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>59467</t>
+          <t>60224</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>77472</t>
+          <t>78643</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>49,0%</t>
+          <t>49,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>63,84%</t>
+          <t>64,81%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17730</t>
+          <t>17722</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>30337</t>
+          <t>30900</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>47,84%</t>
+          <t>48,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12468</t>
+          <t>12182</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23990</t>
+          <t>24171</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,41%</t>
+          <t>41,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>33802</t>
+          <t>33768</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>50890</t>
+          <t>51101</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>42,11%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>690</t>
+          <t>704</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6462</t>
+          <t>6401</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1905</t>
+          <t>1818</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9199</t>
+          <t>9761</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3580</t>
+          <t>3744</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>13202</t>
+          <t>13455</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>11,09%</t>
         </is>
       </c>
     </row>
@@ -5434,7 +5434,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5545</t>
+          <t>5533</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5449,7 +5449,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5469,7 +5469,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5755</t>
+          <t>5461</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5484,7 +5484,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -5512,7 +5512,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5163</t>
+          <t>5262</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5527,7 +5527,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4949</t>
+          <t>4576</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,77%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>145184</t>
+          <t>145896</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>174149</t>
+          <t>175147</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>45,2%</t>
+          <t>45,42%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>54,22%</t>
+          <t>54,53%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>161335</t>
+          <t>161566</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>190649</t>
+          <t>190103</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>48,72%</t>
+          <t>48,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>57,57%</t>
+          <t>57,4%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>315991</t>
+          <t>314271</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>358765</t>
+          <t>359237</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>48,44%</t>
+          <t>48,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>54,99%</t>
+          <t>55,07%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>116830</t>
+          <t>117363</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>146290</t>
+          <t>145733</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>45,54%</t>
+          <t>45,37%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>107860</t>
+          <t>107595</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>135649</t>
+          <t>135452</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>40,96%</t>
+          <t>40,9%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>233344</t>
+          <t>233393</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>274072</t>
+          <t>274732</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>42,11%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>14104</t>
+          <t>13996</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>28708</t>
+          <t>28683</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>20542</t>
+          <t>20927</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>37259</t>
+          <t>37183</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>39665</t>
+          <t>38062</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>61503</t>
+          <t>60435</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,26%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1767</t>
+          <t>1686</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>9650</t>
+          <t>9368</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1774</t>
+          <t>1718</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>9171</t>
+          <t>8862</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4544</t>
+          <t>4828</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>14514</t>
+          <t>15202</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1421</t>
+          <t>1442</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>8832</t>
+          <t>8708</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6229,7 +6229,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4534</t>
+          <t>4650</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2099</t>
+          <t>2247</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>10680</t>
+          <t>10721</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6274,7 +6274,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6455,7 +6455,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de ayudarse entre los amigos en 2016 (tasa de respuesta: 98,43%)</t>
+          <t>Menores según la frecuencia de ayudarse entre los/as amigos/as, percibida por el adulto en 2016 (tasa de respuesta: 98,43%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6650,12 +6650,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13333</t>
+          <t>12836</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22496</t>
+          <t>22102</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6665,12 +6665,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>70,71%</t>
+          <t>69,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6685,12 +6685,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6937</t>
+          <t>6973</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16399</t>
+          <t>16346</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,76%</t>
+          <t>44,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>23257</t>
+          <t>22187</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>36164</t>
+          <t>36084</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>32,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,83%</t>
+          <t>52,71%</t>
         </is>
       </c>
     </row>
@@ -6763,12 +6763,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8381</t>
+          <t>8414</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16905</t>
+          <t>17137</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6778,12 +6778,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>53,14%</t>
+          <t>53,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6798,12 +6798,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15238</t>
+          <t>15216</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25196</t>
+          <t>24862</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>41,59%</t>
+          <t>41,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>68,77%</t>
+          <t>67,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>26617</t>
+          <t>25637</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>39033</t>
+          <t>39451</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>38,88%</t>
+          <t>37,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>57,02%</t>
+          <t>57,63%</t>
         </is>
       </c>
     </row>
@@ -6881,7 +6881,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4935</t>
+          <t>5291</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6896,7 +6896,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2182</t>
+          <t>2277</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9049</t>
+          <t>9770</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3307</t>
+          <t>3053</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>11566</t>
+          <t>11739</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>17,15%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>129268</t>
+          <t>128697</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>155708</t>
+          <t>155705</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7347,7 +7347,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>52,02%</t>
+          <t>51,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>125835</t>
+          <t>126040</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>152279</t>
+          <t>151684</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>51,45%</t>
+          <t>51,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>62,27%</t>
+          <t>62,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>262014</t>
+          <t>263132</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>300549</t>
+          <t>298889</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>53,14%</t>
+          <t>53,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,96%</t>
+          <t>60,62%</t>
         </is>
       </c>
     </row>
@@ -7445,12 +7445,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>63542</t>
+          <t>62189</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>87501</t>
+          <t>86397</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>71405</t>
+          <t>72676</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>95845</t>
+          <t>97004</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7495,12 +7495,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>39,19%</t>
+          <t>39,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>141073</t>
+          <t>140965</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>176317</t>
+          <t>174945</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>35,48%</t>
         </is>
       </c>
     </row>
@@ -7558,12 +7558,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>19256</t>
+          <t>19906</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>35929</t>
+          <t>36184</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>12308</t>
+          <t>12600</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>26239</t>
+          <t>27225</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>36018</t>
+          <t>35501</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>56496</t>
+          <t>57694</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,7%</t>
         </is>
       </c>
     </row>
@@ -7671,12 +7671,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1466</t>
+          <t>1547</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9764</t>
+          <t>9113</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7686,12 +7686,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7711,7 +7711,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6319</t>
+          <t>5596</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7726,7 +7726,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2968</t>
+          <t>2799</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11575</t>
+          <t>11810</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3935</t>
+          <t>4128</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7804,7 +7804,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7824,7 +7824,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4445</t>
+          <t>4625</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7839,7 +7839,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7859,7 +7859,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4694</t>
+          <t>4817</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,98%</t>
         </is>
       </c>
     </row>
@@ -8014,12 +8014,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>34208</t>
+          <t>33668</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>48711</t>
+          <t>47714</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8029,12 +8029,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>45,98%</t>
+          <t>45,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>65,47%</t>
+          <t>64,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>45306</t>
+          <t>44668</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>58845</t>
+          <t>58980</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>58,04%</t>
+          <t>57,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>75,38%</t>
+          <t>75,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>82458</t>
+          <t>82335</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>103143</t>
+          <t>103022</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>54,09%</t>
+          <t>54,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>67,65%</t>
+          <t>67,57%</t>
         </is>
       </c>
     </row>
@@ -8127,12 +8127,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21663</t>
+          <t>22580</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>35652</t>
+          <t>36549</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>47,92%</t>
+          <t>49,13%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15815</t>
+          <t>15775</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>28589</t>
+          <t>29147</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8177,12 +8177,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>42191</t>
+          <t>41935</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>61259</t>
+          <t>60741</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,18%</t>
+          <t>39,84%</t>
         </is>
       </c>
     </row>
@@ -8240,12 +8240,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1507</t>
+          <t>1782</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8639</t>
+          <t>8687</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8255,12 +8255,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>638</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5307</t>
+          <t>5927</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8290,12 +8290,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2817</t>
+          <t>3135</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>11206</t>
+          <t>11267</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,39%</t>
         </is>
       </c>
     </row>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3106</t>
+          <t>3243</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8373,7 +8373,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8393,7 +8393,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4946</t>
+          <t>4835</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8408,7 +8408,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>548</t>
+          <t>551</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5566</t>
+          <t>6475</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8443,7 +8443,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>4,25%</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>186121</t>
+          <t>187710</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>217365</t>
+          <t>216261</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8711,12 +8711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>52,47%</t>
+          <t>52,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>61,28%</t>
+          <t>60,97%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>186005</t>
+          <t>185946</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>218520</t>
+          <t>217062</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>51,77%</t>
+          <t>51,76%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>60,82%</t>
+          <t>60,42%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>380451</t>
+          <t>382305</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>424121</t>
+          <t>425804</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>53,29%</t>
+          <t>53,55%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>59,4%</t>
+          <t>59,64%</t>
         </is>
       </c>
     </row>
@@ -8809,12 +8809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>100722</t>
+          <t>100133</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>129039</t>
+          <t>129206</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>111992</t>
+          <t>111627</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>142218</t>
+          <t>142207</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>39,59%</t>
+          <t>39,58%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>221450</t>
+          <t>220659</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>262250</t>
+          <t>263300</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>36,88%</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>23663</t>
+          <t>23680</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>41923</t>
+          <t>42420</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>18224</t>
+          <t>18563</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>34803</t>
+          <t>35150</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>46788</t>
+          <t>47572</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>70583</t>
+          <t>72876</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>10,21%</t>
         </is>
       </c>
     </row>
@@ -9035,12 +9035,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1987</t>
+          <t>1727</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>10594</t>
+          <t>9888</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9050,12 +9050,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9070,12 +9070,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1240</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7676</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9090,7 +9090,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4318</t>
+          <t>4347</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>15434</t>
+          <t>14972</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -9153,7 +9153,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3678</t>
+          <t>4305</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9168,7 +9168,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9188,7 +9188,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4471</t>
+          <t>4535</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9203,7 +9203,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9223,7 +9223,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5616</t>
+          <t>4667</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9238,7 +9238,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,65%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP07A16-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP07A16-Estudios-trans_orig.xlsx
@@ -537,13 +537,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de ayudarse entre los/as amigos/as, percibida por el adulto en 2007 (tasa de respuesta: 99,2%)</t>
+          <t>Menores según la frecuencia de ayudarse entre los/as amigos/as, percibida por el/la adulto/a [KIDSCREEN 20] en 2007 (tasa de respuesta: 99,2%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>24881</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>19507</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>30930</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>52,68%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>41,3%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>65,49%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>25716</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>19824</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>30835</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>20276</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>31679</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>51,39%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>39,62%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>61,62%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>24881</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>19362</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>30141</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>52,68%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>40,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>63,82%</t>
+          <t>63,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>43194</t>
+          <t>42768</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>58866</t>
+          <t>58463</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>43,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>60,52%</t>
+          <t>60,1%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>18909</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>13538</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>24758</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>40,04%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>28,66%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>52,42%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>19538</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>14230</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>25569</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>13829</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>25192</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>39,04%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>28,44%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>51,1%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>18909</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>13649</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>24994</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>40,04%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,92%</t>
+          <t>50,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>30867</t>
+          <t>31021</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>46749</t>
+          <t>46707</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>31,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>48,06%</t>
+          <t>48,02%</t>
         </is>
       </c>
     </row>
@@ -948,92 +948,92 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>3440</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1358</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>6947</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>7,28%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>2,88%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>14,71%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>4103</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1360</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>8365</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>1540</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>8303</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>8,2%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>2,72%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>16,72%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>3440</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>1361</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>3,08%</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>16,59%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
         <is>
           <t>7543</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>7,28%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>2,88%</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>15,97%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>7543</t>
-        </is>
-      </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4027</t>
+          <t>3975</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13256</t>
+          <t>12291</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>12,64%</t>
         </is>
       </c>
     </row>
@@ -1061,107 +1061,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>683</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3432</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4299</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,37%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>6,86%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>8,59%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>683</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>3365</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>683</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>3446</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -1287,57 +1287,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>47230</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>47230</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>47230</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>50041</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>50041</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>50041</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>47230</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>47230</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>47230</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1404,72 +1404,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>116117</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>103324</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>129164</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>48,94%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>43,55%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>54,44%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>157</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>104160</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>92649</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>115333</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>93153</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>116449</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>51,39%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>45,71%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>56,91%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>175</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>116117</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>104033</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>128741</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>48,94%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>45,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>54,26%</t>
+          <t>57,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>202844</t>
+          <t>203425</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>236535</t>
+          <t>236506</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>46,11%</t>
+          <t>46,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>53,77%</t>
+          <t>53,76%</t>
         </is>
       </c>
     </row>
@@ -1517,72 +1517,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>98020</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>86423</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>111549</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>41,31%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>36,42%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>47,01%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>74267</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>64151</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>84474</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>63136</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>85673</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>36,64%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>31,65%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>41,68%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>98020</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>86333</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>110123</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>41,31%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>46,41%</t>
+          <t>42,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>155344</t>
+          <t>156208</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>189588</t>
+          <t>188203</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>35,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>43,09%</t>
+          <t>42,78%</t>
         </is>
       </c>
     </row>
@@ -1635,67 +1635,67 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>21996</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>15796</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>30821</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>9,27%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>6,66%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>12,99%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
           <t>22344</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>16172</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>30772</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>16398</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>30000</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>11,03%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>7,98%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>15,18%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>21996</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>15596</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>30429</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>9,27%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>34736</t>
+          <t>35179</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>55363</t>
+          <t>56282</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,79%</t>
         </is>
       </c>
     </row>
@@ -1743,92 +1743,92 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>487</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2073</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,21%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>0,87%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1267</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3992</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4547</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,63%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>1,97%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>2,24%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>1754</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>487</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>2800</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1754</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>489</t>
-        </is>
-      </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4996</t>
+          <t>4902</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,11%</t>
         </is>
       </c>
     </row>
@@ -1861,102 +1861,102 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>3223</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1,36%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
           <t>632</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>3258</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>3168</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,31%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>1,61%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>647</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>1,56%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1280</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>3879</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>4470</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1280</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>4928</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,02%</t>
         </is>
       </c>
     </row>
@@ -1969,57 +1969,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>358</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>237268</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>237268</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>237268</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>303</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>202670</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>202670</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>202670</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>358</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>237268</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>237268</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>237268</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2086,72 +2086,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>24330</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>18514</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>30937</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>40,72%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>30,99%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>51,78%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>24677</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>18746</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>31534</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>18436</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>31210</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>36,91%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>28,04%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>47,17%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>24330</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>18227</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>30510</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>40,72%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>51,07%</t>
+          <t>46,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>40487</t>
+          <t>40362</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>57951</t>
+          <t>58503</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>46,21%</t>
         </is>
       </c>
     </row>
@@ -2199,72 +2199,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>28477</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>22290</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>34916</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>47,66%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>37,31%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>58,44%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>31762</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>25435</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>38773</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>25448</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>38587</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>47,51%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>38,05%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>58,0%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>28477</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>22106</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>34821</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>47,66%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>37,0%</t>
+          <t>38,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>58,28%</t>
+          <t>57,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>51290</t>
+          <t>50551</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>69027</t>
+          <t>69303</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>40,51%</t>
+          <t>39,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>54,52%</t>
+          <t>54,74%</t>
         </is>
       </c>
     </row>
@@ -2312,72 +2312,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>6938</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>3367</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>11719</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>11,61%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>5,64%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>19,61%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>9762</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>5868</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>15009</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>5714</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>15222</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>14,6%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>8,78%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>22,45%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>6938</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>3478</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>11767</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>11,61%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>10974</t>
+          <t>11759</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>24139</t>
+          <t>24506</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,36%</t>
         </is>
       </c>
     </row>
@@ -2425,107 +2425,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>654</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>3208</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>2731</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,98%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>4,8%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>4,08%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>654</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>3284</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>654</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>2927</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -2651,57 +2651,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>59745</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>59745</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>59745</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>96</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>66854</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>66854</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>66854</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>59745</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>59745</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>59745</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2768,72 +2768,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>249</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>165328</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>150600</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>179766</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>48,03%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>43,75%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>52,22%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>231</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>154553</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>141130</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>170443</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>141269</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>169210</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>48,36%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>44,16%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>53,34%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>249</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>165328</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>150567</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>180296</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>48,03%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>43,74%</t>
+          <t>44,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>52,37%</t>
+          <t>52,95%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>299590</t>
+          <t>298752</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>341172</t>
+          <t>340931</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>45,13%</t>
+          <t>45,01%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>51,4%</t>
+          <t>51,36%</t>
         </is>
       </c>
     </row>
@@ -2881,72 +2881,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>145406</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>130878</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>159184</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>42,24%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>38,02%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>46,24%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>184</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>125567</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>111218</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>139471</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>111288</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>138973</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>39,29%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>34,8%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>43,64%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>217</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>145406</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>129794</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>159506</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>42,24%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>46,34%</t>
+          <t>43,49%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>250093</t>
+          <t>251704</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>292935</t>
+          <t>292512</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>37,92%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>44,07%</t>
         </is>
       </c>
     </row>
@@ -2994,72 +2994,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>32374</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>24047</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>42063</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>9,4%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>6,99%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>12,22%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>36209</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>27152</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>45400</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>27531</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>46387</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>11,33%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>8,5%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>14,21%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>32374</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>24018</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>40815</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>9,4%</t>
-        </is>
-      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>56509</t>
+          <t>56541</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>81764</t>
+          <t>82268</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,39%</t>
         </is>
       </c>
     </row>
@@ -3107,72 +3107,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>487</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>2443</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0,14%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>0,71%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>2604</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>686</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>6035</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>687</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>6251</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>0,81%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>0,21%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>1,89%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>487</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>3123</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>0,14%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1143</t>
+          <t>1173</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>7208</t>
+          <t>6981</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -3225,102 +3225,102 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>2605</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>0,76%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
           <t>632</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>3788</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>3527</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>0,2%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>1,19%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>647</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>1280</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>3256</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>4500</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
         <is>
           <t>0,19%</t>
         </is>
       </c>
-      <c r="O26" s="2" t="inlineStr">
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>0,95%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>1280</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>5113</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,68%</t>
         </is>
       </c>
     </row>
@@ -3333,57 +3333,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>517</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>344243</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>344243</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>344243</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>474</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>319566</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>319566</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>319566</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>517</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>344243</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>344243</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>344243</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3496,13 +3496,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de ayudarse entre los/as amigos/as, percibida por el adulto en 2012 (tasa de respuesta: 97,81%)</t>
+          <t>Menores según la frecuencia de ayudarse entre los/as amigos/as, percibida por el/la adulto/a [KIDSCREEN 20] en 2012 (tasa de respuesta: 97,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3513,7 +3513,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3681,72 +3681,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>24258</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>18878</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>29434</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>52,9%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>41,17%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>64,19%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>28629</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>22229</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>34651</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>22288</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>34478</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>54,67%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>42,45%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>66,17%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>24258</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>18669</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>29345</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>52,9%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>42,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>64,0%</t>
+          <t>65,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>44261</t>
+          <t>44565</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>60747</t>
+          <t>61119</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>45,06%</t>
+          <t>45,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>61,85%</t>
+          <t>62,23%</t>
         </is>
       </c>
     </row>
@@ -3794,72 +3794,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>18429</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>13504</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>24380</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>40,19%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>29,45%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>53,17%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>16455</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>11140</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>22021</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>11855</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>22801</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>31,42%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>21,27%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>42,05%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>18429</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>13598</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>24186</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>40,19%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,75%</t>
+          <t>43,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>27232</t>
+          <t>26981</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>43389</t>
+          <t>42939</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>44,18%</t>
+          <t>43,72%</t>
         </is>
       </c>
     </row>
@@ -3907,72 +3907,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>3166</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1243</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>7007</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>6,9%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>2,71%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>15,28%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>5566</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2514</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>10496</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>2474</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>11126</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>10,63%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>4,8%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>20,04%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>3166</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>1236</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>6538</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>6,9%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4666</t>
+          <t>4863</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13835</t>
+          <t>15200</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>15,48%</t>
         </is>
       </c>
     </row>
@@ -4020,107 +4020,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1714</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>6188</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5445</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>3,27%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>11,82%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>10,4%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>1714</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>5746</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>1,75%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1714</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>6083</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>1,75%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>5,85%</t>
         </is>
       </c>
     </row>
@@ -4246,57 +4246,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>45853</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>45853</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>45853</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>74</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>52364</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>52364</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>52364</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>45853</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>45853</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>45853</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4363,72 +4363,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>117653</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>104139</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>128748</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>51,74%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>45,8%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>56,62%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>136</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>96888</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>85282</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>108609</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>85224</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>108837</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>47,17%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>41,52%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>52,87%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>174</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>117653</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>105254</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>131498</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>51,74%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>46,29%</t>
+          <t>41,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>57,83%</t>
+          <t>52,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>197026</t>
+          <t>198647</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>231727</t>
+          <t>229695</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>45,52%</t>
+          <t>45,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>53,54%</t>
+          <t>53,07%</t>
         </is>
       </c>
     </row>
@@ -4476,72 +4476,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>85356</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>74175</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>97907</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>37,54%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>32,62%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>43,06%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>132</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>91033</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>78578</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>103007</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>79190</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>103126</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>44,32%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>38,25%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>50,15%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>85356</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>72133</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>97859</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>37,54%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>38,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>43,04%</t>
+          <t>50,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>160098</t>
+          <t>160901</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>196147</t>
+          <t>193537</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>37,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>45,32%</t>
+          <t>44,72%</t>
         </is>
       </c>
     </row>
@@ -4589,72 +4589,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>20439</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>13890</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>28924</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>8,99%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>6,11%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>12,72%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>12611</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>7560</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>18578</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>7909</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>19420</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>6,14%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>3,68%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>9,04%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>20439</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>14160</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>28047</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>8,99%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>24601</t>
+          <t>25186</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>42502</t>
+          <t>43056</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,95%</t>
         </is>
       </c>
     </row>
@@ -4707,67 +4707,67 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>2642</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>6441</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,16%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,83%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>2611</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>702</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>6623</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>6565</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,27%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,34%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,22%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>2642</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>845</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>6158</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,16%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2493</t>
+          <t>2171</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10817</t>
+          <t>10027</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -4815,72 +4815,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1298</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>3950</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1,74%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>2275</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>666</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>6510</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>654</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>6164</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>1,11%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,32%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>3,17%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>1298</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>4492</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1312</t>
+          <t>1322</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>8415</t>
+          <t>8057</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -4928,57 +4928,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>227388</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>227388</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>227388</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>294</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>205418</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>205418</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>205418</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>332</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>227388</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>227388</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>227388</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5045,72 +5045,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>33612</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>27690</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>39897</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>58,02%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>47,8%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>68,87%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>35468</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>28006</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>42022</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>28476</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>42191</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>55,93%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>44,16%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>66,26%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>33612</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>27433</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>40068</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>58,02%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>47,35%</t>
+          <t>44,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>69,16%</t>
+          <t>66,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>60224</t>
+          <t>59870</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>78643</t>
+          <t>77849</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>49,63%</t>
+          <t>49,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>64,81%</t>
+          <t>64,15%</t>
         </is>
       </c>
     </row>
@@ -5158,72 +5158,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>18014</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>12973</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>23987</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>31,09%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>22,39%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>41,4%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>23749</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>17722</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>30900</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>17605</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>30677</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>37,45%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>27,94%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>48,72%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>18014</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>12182</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>24171</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>31,09%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,72%</t>
+          <t>48,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>33768</t>
+          <t>33635</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>51101</t>
+          <t>51037</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>42,11%</t>
+          <t>42,06%</t>
         </is>
       </c>
     </row>
@@ -5271,72 +5271,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>4643</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>2046</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>9836</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>8,01%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>3,53%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>16,98%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>2716</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>704</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>6401</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>729</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>6779</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>4,28%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>10,09%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>4643</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>1818</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>9761</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>8,01%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3744</t>
+          <t>3998</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>13455</t>
+          <t>13653</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,25%</t>
         </is>
       </c>
     </row>
@@ -5384,107 +5384,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>1664</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>5729</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>2,87%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>9,89%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>1664</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>5533</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>2,87%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>6080</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>1,37%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>9,55%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>1664</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>5461</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>1,37%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>5,01%</t>
         </is>
       </c>
     </row>
@@ -5497,107 +5497,107 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>1485</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>5262</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>4484</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>2,34%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>8,3%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>7,07%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>1485</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>5075</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>1,22%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>1485</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>4576</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>1,22%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>4,18%</t>
         </is>
       </c>
     </row>
@@ -5610,57 +5610,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>57933</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>57933</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>57933</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>63418</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>63418</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>63418</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>57933</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>57933</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>57933</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5727,72 +5727,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>175523</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>159073</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>189704</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>53,0%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>48,03%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>57,28%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>227</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>160985</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>145896</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>175147</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>146417</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>175495</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>50,12%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>45,42%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>54,53%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>260</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>175523</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>161566</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>190103</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>53,0%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>48,79%</t>
+          <t>45,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>57,4%</t>
+          <t>54,64%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>314271</t>
+          <t>316580</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>359237</t>
+          <t>357149</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>48,53%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>55,07%</t>
+          <t>54,75%</t>
         </is>
       </c>
     </row>
@@ -5840,72 +5840,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>121799</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>107282</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>136526</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>36,78%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>32,39%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>41,22%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>188</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>131237</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>117363</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>145733</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>116690</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>144602</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>40,86%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>36,54%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>45,37%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>173</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>121799</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>107595</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>135452</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>36,78%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>45,02%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>233393</t>
+          <t>234619</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>274732</t>
+          <t>274482</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>42,11%</t>
+          <t>42,07%</t>
         </is>
       </c>
     </row>
@@ -5953,72 +5953,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>28247</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>20318</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>37017</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>8,53%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>6,14%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>11,18%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>20893</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>13996</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>28683</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>13702</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>28419</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>6,5%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>4,36%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>8,93%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>28247</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>20927</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>37183</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>8,53%</t>
-        </is>
-      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>38062</t>
+          <t>39165</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>60435</t>
+          <t>59960</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,19%</t>
         </is>
       </c>
     </row>
@@ -6071,69 +6071,69 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
+          <t>4306</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>1526</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>9314</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>2,81%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
           <t>4325</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>1686</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>9368</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>1712</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>9386</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>1,35%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>0,53%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
         <is>
           <t>2,92%</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>4306</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>1718</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>8862</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>2,68%</t>
-        </is>
-      </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
           <t>12</t>
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4828</t>
+          <t>4701</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>15202</t>
+          <t>14966</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -6179,72 +6179,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>1298</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>4285</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>1,29%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>3760</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>1442</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>8708</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>1432</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>8448</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>1,17%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>0,45%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>2,71%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>1298</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>4650</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2247</t>
+          <t>2071</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>10721</t>
+          <t>10024</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,54%</t>
         </is>
       </c>
     </row>
@@ -6292,57 +6292,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>482</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>331174</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>331174</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>331174</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>456</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>321200</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>321200</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>321200</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>482</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>331174</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>331174</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>331174</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6455,13 +6455,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de ayudarse entre los/as amigos/as, percibida por el adulto en 2016 (tasa de respuesta: 98,43%)</t>
+          <t>Menores según la frecuencia de ayudarse entre los/as amigos/as, percibida por el/la adulto/a [KIDSCREEN 20] en 2016 (tasa de respuesta: 98,43%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6472,7 +6472,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6640,72 +6640,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>11176</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>6727</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>16093</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>30,51%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>18,36%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>43,92%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>17785</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>12836</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>22102</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>12957</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>22644</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>55,9%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>40,35%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>69,47%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>11176</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>6973</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>16346</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>30,51%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>40,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,61%</t>
+          <t>71,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22187</t>
+          <t>21885</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>36084</t>
+          <t>36036</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,71%</t>
+          <t>52,64%</t>
         </is>
       </c>
     </row>
@@ -6753,72 +6753,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>20415</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>15284</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>25326</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>55,72%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>41,72%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>69,12%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>12549</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>8414</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>17137</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>8156</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>17290</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>39,44%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>26,45%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>53,87%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>20415</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>15216</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>24862</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>55,72%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>41,53%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>67,86%</t>
+          <t>54,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>25637</t>
+          <t>26290</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>39451</t>
+          <t>39304</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>57,63%</t>
+          <t>57,42%</t>
         </is>
       </c>
     </row>
@@ -6866,72 +6866,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>5046</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2476</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>9354</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>13,77%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>6,76%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>25,53%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>1481</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>5291</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>5514</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>4,65%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>16,63%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>5046</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>2277</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>9770</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>13,77%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>6,21%</t>
-        </is>
-      </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3053</t>
+          <t>3102</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>11739</t>
+          <t>11615</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>16,97%</t>
         </is>
       </c>
     </row>
@@ -7205,57 +7205,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>36638</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>36638</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>36638</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>31814</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>31814</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>31814</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>36638</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>36638</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>36638</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7322,72 +7322,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>139044</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>127061</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>152003</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>56,85%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>51,95%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>62,15%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>205</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>142498</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>128697</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>155705</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>130186</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>156010</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>57,35%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>51,79%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>62,66%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>189</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>139044</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>126040</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>151684</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>56,85%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>51,54%</t>
+          <t>52,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>62,02%</t>
+          <t>62,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>263132</t>
+          <t>263241</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>298889</t>
+          <t>299489</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>53,37%</t>
+          <t>53,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,62%</t>
+          <t>60,74%</t>
         </is>
       </c>
     </row>
@@ -7435,72 +7435,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>83936</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>72067</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>95560</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>34,32%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>29,47%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>39,07%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>74110</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>62189</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>86397</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>62997</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>86649</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>29,82%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>25,03%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>34,77%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>83936</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>72676</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>97004</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>34,32%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>39,66%</t>
+          <t>34,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>140965</t>
+          <t>140393</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>174945</t>
+          <t>175428</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>35,58%</t>
         </is>
       </c>
     </row>
@@ -7548,72 +7548,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>18697</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>12596</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>26820</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>7,65%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>5,15%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>10,97%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>26869</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>19906</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>36184</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>19282</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>36626</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>10,81%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>8,01%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>14,56%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>18697</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>12600</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>27225</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>7,65%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>35501</t>
+          <t>35837</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>57694</t>
+          <t>57717</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,71%</t>
         </is>
       </c>
     </row>
@@ -7661,72 +7661,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2098</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5726</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,86%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,34%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>4285</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1547</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>9113</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1488</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>10111</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,72%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,67%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>2098</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>643</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5596</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2799</t>
+          <t>2738</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11810</t>
+          <t>11609</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -7779,102 +7779,102 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>790</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>4238</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1,73%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
           <t>724</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>4128</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>4338</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,29%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>1,66%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>790</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>1,75%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1513</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>4625</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>5375</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,31%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>1,89%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1513</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>4817</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,09%</t>
         </is>
       </c>
     </row>
@@ -7887,57 +7887,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>334</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>244565</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>244565</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>244565</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>357</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>248486</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>248486</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>248486</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>334</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>244565</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>244565</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>244565</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8004,72 +8004,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>52272</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>45254</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>59255</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>66,96%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>57,97%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>75,91%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>40864</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>33668</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>47714</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>33909</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>47766</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>54,93%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>45,25%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>64,13%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>52272</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>44668</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>58980</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>66,96%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>57,22%</t>
+          <t>45,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>75,56%</t>
+          <t>64,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>82335</t>
+          <t>82402</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>103022</t>
+          <t>102468</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>54,0%</t>
+          <t>54,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>67,57%</t>
+          <t>67,21%</t>
         </is>
       </c>
     </row>
@@ -8117,72 +8117,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>22298</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>15988</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>29190</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>28,56%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>20,48%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>37,39%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>28850</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>22580</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>36549</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>22712</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>36328</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>38,78%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>30,35%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>49,13%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>22298</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>15775</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>29147</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>28,56%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>48,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>41935</t>
+          <t>41811</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>60741</t>
+          <t>60876</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>39,93%</t>
         </is>
       </c>
     </row>
@@ -8230,72 +8230,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>2052</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>629</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>5553</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>2,63%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0,81%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>7,11%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>4057</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>1782</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>8687</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>1382</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>7824</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>5,45%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>2,39%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>11,68%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>2052</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>638</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>5927</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>2,63%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3135</t>
+          <t>3165</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>11267</t>
+          <t>11449</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,51%</t>
         </is>
       </c>
     </row>
@@ -8343,72 +8343,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>1440</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>4917</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1,84%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>6,3%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>626</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>3243</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>4029</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,84%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>4,36%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>1440</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>4835</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>1,84%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>546</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6475</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8443,7 +8443,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>3,96%</t>
         </is>
       </c>
     </row>
@@ -8569,57 +8569,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>78061</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>78061</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>78061</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>74398</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>74398</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>74398</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>78061</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>78061</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>78061</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8686,72 +8686,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>202492</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>186401</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>217787</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>56,36%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>51,88%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>60,62%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>286</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>201147</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>187710</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>216261</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>186788</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>218359</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>56,71%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>52,92%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>60,97%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>276</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>202492</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>185946</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>217062</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>56,36%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>52,66%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>60,42%</t>
+          <t>61,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>382305</t>
+          <t>380450</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>425804</t>
+          <t>425342</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>53,55%</t>
+          <t>53,29%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>59,64%</t>
+          <t>59,57%</t>
         </is>
       </c>
     </row>
@@ -8799,72 +8799,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>126650</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>111139</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>141634</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>35,25%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>30,94%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>39,42%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>169</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>115509</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>100133</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>129206</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>100526</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>130922</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>32,57%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>28,23%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>36,43%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>174</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>126650</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>111627</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>142207</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>35,25%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>39,58%</t>
+          <t>36,91%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>220659</t>
+          <t>219393</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>263300</t>
+          <t>263587</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>36,92%</t>
         </is>
       </c>
     </row>
@@ -8912,72 +8912,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>25795</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>18801</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>34869</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>7,18%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>5,23%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>9,71%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>32407</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>23680</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>42420</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>24241</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>42601</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>9,14%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>6,68%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>11,96%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>25795</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>18563</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>35150</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>7,18%</t>
-        </is>
-      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>47572</t>
+          <t>47020</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>72876</t>
+          <t>72048</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,09%</t>
         </is>
       </c>
     </row>
@@ -9025,72 +9025,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>3538</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>1314</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>8007</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>2,23%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>4911</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>1727</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>9888</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>1767</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>10411</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>1,38%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>2,79%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>3538</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>1240</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>8664</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4347</t>
+          <t>4376</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>14972</t>
+          <t>15345</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9125,7 +9125,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -9143,102 +9143,102 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>790</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>3700</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>1,03%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
           <t>724</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>4305</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>3571</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>0,2%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>1,21%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>790</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>1,01%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>1513</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>4535</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>5439</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>0,21%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>1,26%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>1513</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>4667</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,76%</t>
         </is>
       </c>
     </row>
@@ -9251,57 +9251,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>493</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>359264</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>359264</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>359264</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>507</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>354698</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>354698</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>354698</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>493</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>359264</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>359264</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>359264</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
